--- a/tame_output/ON/bt/strategyON_20231230.xlsx
+++ b/tame_output/ON/bt/strategyON_20231230.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>93.5%</t>
+          <t>93.7%</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-27.8%</t>
+          <t>-27.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>77.2%</t>
+          <t>77.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -939,7 +939,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -954,11 +954,11 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -977,12 +977,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-27.4%</t>
+          <t>-27.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-15.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>481.5%</t>
+          <t>481.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-161.0%</t>
+          <t>-160.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1064,12 +1064,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1107,11 +1107,11 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2023-11-25</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1130,12 +1130,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-19.3%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-19.1%</t>
+          <t>-19.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1207,17 +1207,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1298,17 +1298,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1318,12 +1318,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>87.9%</t>
+          <t>88.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-33.8%</t>
+          <t>-28.1%</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>111.9%</t>
+          <t>113.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>106.9%</t>
+          <t>108.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.4%</t>
+          <t>-14.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>10.6%</t>
         </is>
       </c>
     </row>
@@ -42755,16 +42755,16 @@
         <v>3.071969877157259</v>
       </c>
       <c r="D1793" t="n">
-        <v>-4.142830039547698</v>
+        <v>-4.199737445047185</v>
       </c>
       <c r="E1793" t="n">
-        <v>1.414481437024434</v>
+        <v>1.391718474824639</v>
       </c>
       <c r="F1793" t="n">
-        <v>-0.2391449650824606</v>
+        <v>-0.2392257379731304</v>
       </c>
       <c r="G1793" t="n">
-        <v>2.928482898107785</v>
+        <v>2.928434434373383</v>
       </c>
     </row>
     <row r="1794">
@@ -42778,16 +42778,16 @@
         <v>3.076099785321473</v>
       </c>
       <c r="D1794" t="n">
-        <v>-4.132502042531845</v>
+        <v>-4.189409448031332</v>
       </c>
       <c r="E1794" t="n">
-        <v>1.422742543994988</v>
+        <v>1.399979581795193</v>
       </c>
       <c r="F1794" t="n">
-        <v>-0.2288169680666085</v>
+        <v>-0.2288977409572782</v>
       </c>
       <c r="G1794" t="n">
-        <v>2.938809604481509</v>
+        <v>2.938761140747108</v>
       </c>
     </row>
     <row r="1795">
@@ -42801,16 +42801,16 @@
         <v>3.082620445523309</v>
       </c>
       <c r="D1795" t="n">
-        <v>-4.132385707384289</v>
+        <v>-4.189293112883776</v>
       </c>
       <c r="E1795" t="n">
-        <v>1.429309738255847</v>
+        <v>1.406546776056052</v>
       </c>
       <c r="F1795" t="n">
-        <v>-0.2287006329190527</v>
+        <v>-0.2287814058097225</v>
       </c>
       <c r="G1795" t="n">
-        <v>2.945400065771879</v>
+        <v>2.945351602037477</v>
       </c>
     </row>
     <row r="1796">
@@ -42824,16 +42824,16 @@
         <v>3.079594415968698</v>
       </c>
       <c r="D1796" t="n">
-        <v>-4.134231116961157</v>
+        <v>-4.191138522460644</v>
       </c>
       <c r="E1796" t="n">
-        <v>1.425545544870488</v>
+        <v>1.402782582670693</v>
       </c>
       <c r="F1796" t="n">
-        <v>-0.2287006329190527</v>
+        <v>-0.2287814058097225</v>
       </c>
       <c r="G1796" t="n">
-        <v>2.942374036217268</v>
+        <v>2.942325572482866</v>
       </c>
     </row>
     <row r="1797">
@@ -42847,16 +42847,16 @@
         <v>3.079532703829831</v>
       </c>
       <c r="D1797" t="n">
-        <v>-4.132732684436058</v>
+        <v>-4.189640089935545</v>
       </c>
       <c r="E1797" t="n">
-        <v>1.426083205741661</v>
+        <v>1.403320243541866</v>
       </c>
       <c r="F1797" t="n">
-        <v>-0.2272022003939538</v>
+        <v>-0.2272829732846236</v>
       </c>
       <c r="G1797" t="n">
-        <v>2.943211383593461</v>
+        <v>2.943162919859059</v>
       </c>
     </row>
     <row r="1798">
@@ -42864,22 +42864,22 @@
         <v>45260</v>
       </c>
       <c r="B1798" t="n">
-        <v>3.169279212762261</v>
+        <v>3.16927921276226</v>
       </c>
       <c r="C1798" t="n">
         <v>3.080810681773143</v>
       </c>
       <c r="D1798" t="n">
-        <v>-4.140796936628791</v>
+        <v>-4.197704342128278</v>
       </c>
       <c r="E1798" t="n">
-        <v>1.42413548280788</v>
+        <v>1.401372520608085</v>
       </c>
       <c r="F1798" t="n">
-        <v>-0.2352664525866877</v>
+        <v>-0.2353472254773574</v>
       </c>
       <c r="G1798" t="n">
-        <v>2.939650810221132</v>
+        <v>2.93960234648673</v>
       </c>
     </row>
     <row r="1799">
@@ -42893,16 +42893,16 @@
         <v>3.080810681773143</v>
       </c>
       <c r="D1799" t="n">
-        <v>-4.142126904090004</v>
+        <v>-4.199034309589491</v>
       </c>
       <c r="E1799" t="n">
-        <v>1.423603495823395</v>
+        <v>1.4008405336236</v>
       </c>
       <c r="F1799" t="n">
-        <v>-0.2352664525866877</v>
+        <v>-0.2353472254773574</v>
       </c>
       <c r="G1799" t="n">
-        <v>2.939650810221132</v>
+        <v>2.93960234648673</v>
       </c>
     </row>
     <row r="1800">
@@ -42910,22 +42910,22 @@
         <v>45262</v>
       </c>
       <c r="B1800" t="n">
-        <v>3.199276732583694</v>
+        <v>3.199276732583693</v>
       </c>
       <c r="C1800" t="n">
         <v>3.083027154880305</v>
       </c>
       <c r="D1800" t="n">
-        <v>-3.914262221356493</v>
+        <v>-3.97116962685598</v>
       </c>
       <c r="E1800" t="n">
-        <v>1.516965842023961</v>
+        <v>1.494202879824166</v>
       </c>
       <c r="F1800" t="n">
-        <v>-0.2352664525866877</v>
+        <v>-0.2353472254773574</v>
       </c>
       <c r="G1800" t="n">
-        <v>2.941867283328294</v>
+        <v>2.941818819593892</v>
       </c>
     </row>
     <row r="1801">
@@ -42933,22 +42933,22 @@
         <v>45263</v>
       </c>
       <c r="B1801" t="n">
-        <v>3.238767863742724</v>
+        <v>3.238767863742723</v>
       </c>
       <c r="C1801" t="n">
         <v>3.090561751225397</v>
       </c>
       <c r="D1801" t="n">
-        <v>-3.666160657489276</v>
+        <v>-3.723068062988763</v>
       </c>
       <c r="E1801" t="n">
-        <v>1.62374106391594</v>
+        <v>1.600978101716145</v>
       </c>
       <c r="F1801" t="n">
-        <v>-0.2352664525866877</v>
+        <v>-0.2353472254773574</v>
       </c>
       <c r="G1801" t="n">
-        <v>2.949401879673386</v>
+        <v>2.949353415938984</v>
       </c>
     </row>
     <row r="1802">
@@ -42956,22 +42956,22 @@
         <v>45264</v>
       </c>
       <c r="B1802" t="n">
-        <v>3.260068416589524</v>
+        <v>3.260068416589523</v>
       </c>
       <c r="C1802" t="n">
         <v>3.091984762198855</v>
       </c>
       <c r="D1802" t="n">
-        <v>-3.369322258095946</v>
+        <v>-3.426229663595433</v>
       </c>
       <c r="E1802" t="n">
-        <v>1.74389943464673</v>
+        <v>1.721136472446935</v>
       </c>
       <c r="F1802" t="n">
-        <v>-0.12041196410556</v>
+        <v>-0.1204927369962298</v>
       </c>
       <c r="G1802" t="n">
-        <v>3.01973758373552</v>
+        <v>3.019689120001118</v>
       </c>
     </row>
     <row r="1803">
@@ -42979,22 +42979,22 @@
         <v>45265</v>
       </c>
       <c r="B1803" t="n">
-        <v>3.306739876872957</v>
+        <v>3.306739876872956</v>
       </c>
       <c r="C1803" t="n">
         <v>3.093661836664541</v>
       </c>
       <c r="D1803" t="n">
-        <v>-3.065682701270509</v>
+        <v>-3.122590106769997</v>
       </c>
       <c r="E1803" t="n">
-        <v>1.867032331842591</v>
+        <v>1.844269369642796</v>
       </c>
       <c r="F1803" t="n">
-        <v>-0.12041196410556</v>
+        <v>-0.1204927369962298</v>
       </c>
       <c r="G1803" t="n">
-        <v>3.021414658201207</v>
+        <v>3.021366194466805</v>
       </c>
     </row>
     <row r="1804">
@@ -43002,22 +43002,22 @@
         <v>45266</v>
       </c>
       <c r="B1804" t="n">
-        <v>3.312164595946329</v>
+        <v>3.312164595946328</v>
       </c>
       <c r="C1804" t="n">
         <v>3.089601258113999</v>
       </c>
       <c r="D1804" t="n">
-        <v>-2.776662094829801</v>
+        <v>-2.833569500329288</v>
       </c>
       <c r="E1804" t="n">
-        <v>1.978579995868331</v>
+        <v>1.955817033668537</v>
       </c>
       <c r="F1804" t="n">
-        <v>-0.12041196410556</v>
+        <v>-0.1204927369962298</v>
       </c>
       <c r="G1804" t="n">
-        <v>3.017354079650664</v>
+        <v>3.017305615916262</v>
       </c>
     </row>
     <row r="1805">
@@ -43025,22 +43025,22 @@
         <v>45267</v>
       </c>
       <c r="B1805" t="n">
-        <v>3.300520058336486</v>
+        <v>3.300520058336485</v>
       </c>
       <c r="C1805" t="n">
         <v>3.094821397458016</v>
       </c>
       <c r="D1805" t="n">
-        <v>-2.491942167565904</v>
+        <v>-2.548849573065391</v>
       </c>
       <c r="E1805" t="n">
-        <v>2.097688106117908</v>
+        <v>2.074925143918113</v>
       </c>
       <c r="F1805" t="n">
-        <v>0.1643079631583372</v>
+        <v>0.1642271902676674</v>
       </c>
       <c r="G1805" t="n">
-        <v>3.193406175353021</v>
+        <v>3.193357711618618</v>
       </c>
     </row>
     <row r="1806">
@@ -43048,22 +43048,22 @@
         <v>45268</v>
       </c>
       <c r="B1806" t="n">
-        <v>3.318449829143339</v>
+        <v>3.318449829143338</v>
       </c>
       <c r="C1806" t="n">
         <v>3.100133560631823</v>
       </c>
       <c r="D1806" t="n">
-        <v>-2.208180498074364</v>
+        <v>-2.265087903573851</v>
       </c>
       <c r="E1806" t="n">
-        <v>2.216504937088331</v>
+        <v>2.193741974888536</v>
       </c>
       <c r="F1806" t="n">
-        <v>0.1643079631583372</v>
+        <v>0.1642271902676674</v>
       </c>
       <c r="G1806" t="n">
-        <v>3.198718338526827</v>
+        <v>3.198669874792425</v>
       </c>
     </row>
     <row r="1807">
@@ -43071,22 +43071,22 @@
         <v>45269</v>
       </c>
       <c r="B1807" t="n">
-        <v>3.311781349308503</v>
+        <v>3.311781349308502</v>
       </c>
       <c r="C1807" t="n">
         <v>3.093376148078457</v>
       </c>
       <c r="D1807" t="n">
-        <v>-1.946532103681723</v>
+        <v>-2.00343950918121</v>
       </c>
       <c r="E1807" t="n">
-        <v>2.314406882292021</v>
+        <v>2.291643920092226</v>
       </c>
       <c r="F1807" t="n">
-        <v>0.4259563575509778</v>
+        <v>0.4258755846603081</v>
       </c>
       <c r="G1807" t="n">
-        <v>3.348949962609045</v>
+        <v>3.348901498874643</v>
       </c>
     </row>
     <row r="1808">
@@ -43094,22 +43094,22 @@
         <v>45270</v>
       </c>
       <c r="B1808" t="n">
-        <v>3.271427670257516</v>
+        <v>3.271427670257515</v>
       </c>
       <c r="C1808" t="n">
         <v>3.090839823094569</v>
       </c>
       <c r="D1808" t="n">
-        <v>-1.632365665542391</v>
+        <v>-1.689273071041878</v>
       </c>
       <c r="E1808" t="n">
-        <v>2.437537132563866</v>
+        <v>2.414774170364071</v>
       </c>
       <c r="F1808" t="n">
-        <v>0.7401227956903103</v>
+        <v>0.7400420227996405</v>
       </c>
       <c r="G1808" t="n">
-        <v>3.534913500508757</v>
+        <v>3.534865036774355</v>
       </c>
     </row>
     <row r="1809">
@@ -43117,22 +43117,22 @@
         <v>45271</v>
       </c>
       <c r="B1809" t="n">
-        <v>3.25296238744154</v>
+        <v>3.252962387441539</v>
       </c>
       <c r="C1809" t="n">
         <v>3.109254206721308</v>
       </c>
       <c r="D1809" t="n">
-        <v>-1.509853961436618</v>
+        <v>-1.566761366936106</v>
       </c>
       <c r="E1809" t="n">
-        <v>2.504956197832914</v>
+        <v>2.482193235633119</v>
       </c>
       <c r="F1809" t="n">
-        <v>0.8626344997960826</v>
+        <v>0.8625537269054129</v>
       </c>
       <c r="G1809" t="n">
-        <v>3.62683490659896</v>
+        <v>3.626786442864558</v>
       </c>
     </row>
     <row r="1810">
@@ -43140,22 +43140,22 @@
         <v>45272</v>
       </c>
       <c r="B1810" t="n">
-        <v>3.241257540662168</v>
+        <v>3.241257540662167</v>
       </c>
       <c r="C1810" t="n">
         <v>3.119070330776787</v>
       </c>
       <c r="D1810" t="n">
-        <v>-1.34846542750989</v>
+        <v>-1.405372833009377</v>
       </c>
       <c r="E1810" t="n">
-        <v>2.579327735459084</v>
+        <v>2.55656477325929</v>
       </c>
       <c r="F1810" t="n">
-        <v>1.024023033722811</v>
+        <v>1.023942260832141</v>
       </c>
       <c r="G1810" t="n">
-        <v>3.733484151010475</v>
+        <v>3.733435687276073</v>
       </c>
     </row>
     <row r="1811">
@@ -43163,22 +43163,22 @@
         <v>45273</v>
       </c>
       <c r="B1811" t="n">
-        <v>3.285495323543324</v>
+        <v>3.285495323543323</v>
       </c>
       <c r="C1811" t="n">
         <v>3.132597942828719</v>
       </c>
       <c r="D1811" t="n">
-        <v>-1.168719236361384</v>
+        <v>-1.225626641860871</v>
       </c>
       <c r="E1811" t="n">
-        <v>2.664753823970419</v>
+        <v>2.641990861770624</v>
       </c>
       <c r="F1811" t="n">
-        <v>1.024023033722811</v>
+        <v>1.023942260832141</v>
       </c>
       <c r="G1811" t="n">
-        <v>3.747011763062407</v>
+        <v>3.746963299328005</v>
       </c>
     </row>
     <row r="1812">
@@ -43186,22 +43186,22 @@
         <v>45274</v>
       </c>
       <c r="B1812" t="n">
-        <v>3.287726162978608</v>
+        <v>3.287726162978607</v>
       </c>
       <c r="C1812" t="n">
         <v>3.139185323079984</v>
       </c>
       <c r="D1812" t="n">
-        <v>-1.009918309890161</v>
+        <v>-1.066825715389648</v>
       </c>
       <c r="E1812" t="n">
-        <v>2.734861574810173</v>
+        <v>2.712098612610379</v>
       </c>
       <c r="F1812" t="n">
-        <v>1.024023033722811</v>
+        <v>1.023942260832141</v>
       </c>
       <c r="G1812" t="n">
-        <v>3.753599143313672</v>
+        <v>3.753550679579271</v>
       </c>
     </row>
     <row r="1813">
@@ -43209,22 +43209,22 @@
         <v>45275</v>
       </c>
       <c r="B1813" t="n">
-        <v>3.275586179621267</v>
+        <v>3.275586179621266</v>
       </c>
       <c r="C1813" t="n">
         <v>3.128096071514691</v>
       </c>
       <c r="D1813" t="n">
-        <v>-0.9171298515847839</v>
+        <v>-0.9740372570842712</v>
       </c>
       <c r="E1813" t="n">
-        <v>2.760887706567031</v>
+        <v>2.738124744367236</v>
       </c>
       <c r="F1813" t="n">
-        <v>1.116811492028188</v>
+        <v>1.116730719137518</v>
       </c>
       <c r="G1813" t="n">
-        <v>3.798182966731605</v>
+        <v>3.798134502997203</v>
       </c>
     </row>
     <row r="1814">
@@ -43232,22 +43232,22 @@
         <v>45276</v>
       </c>
       <c r="B1814" t="n">
-        <v>3.268822948291748</v>
+        <v>3.268822948291747</v>
       </c>
       <c r="C1814" t="n">
         <v>3.123696569025415</v>
       </c>
       <c r="D1814" t="n">
-        <v>-0.823109356213942</v>
+        <v>-0.8800167617134294</v>
       </c>
       <c r="E1814" t="n">
-        <v>2.794096402226092</v>
+        <v>2.771333440026297</v>
       </c>
       <c r="F1814" t="n">
-        <v>1.126653932521171</v>
+        <v>1.126573159630502</v>
       </c>
       <c r="G1814" t="n">
-        <v>3.799688928538119</v>
+        <v>3.799640464803717</v>
       </c>
     </row>
     <row r="1815">
@@ -43261,16 +43261,16 @@
         <v>3.109676345532145</v>
       </c>
       <c r="D1815" t="n">
-        <v>-0.7330063883074189</v>
+        <v>-0.7899137938069063</v>
       </c>
       <c r="E1815" t="n">
-        <v>2.816117365895431</v>
+        <v>2.793354403695636</v>
       </c>
       <c r="F1815" t="n">
-        <v>1.129712126808957</v>
+        <v>1.129631353918287</v>
       </c>
       <c r="G1815" t="n">
-        <v>3.787503621617521</v>
+        <v>3.787455157883119</v>
       </c>
     </row>
     <row r="1816">
@@ -43278,22 +43278,22 @@
         <v>45278</v>
       </c>
       <c r="B1816" t="n">
-        <v>3.291576855321623</v>
+        <v>3.291576855321622</v>
       </c>
       <c r="C1816" t="n">
         <v>3.127125924287274</v>
       </c>
       <c r="D1816" t="n">
-        <v>-0.6888772175858437</v>
+        <v>-0.7457846230853311</v>
       </c>
       <c r="E1816" t="n">
-        <v>2.851218612939189</v>
+        <v>2.828455650739395</v>
       </c>
       <c r="F1816" t="n">
-        <v>1.213731299796227</v>
+        <v>1.213650526905557</v>
       </c>
       <c r="G1816" t="n">
-        <v>3.855364704165011</v>
+        <v>3.85531624043061</v>
       </c>
     </row>
     <row r="1817">
@@ -43301,22 +43301,22 @@
         <v>45279</v>
       </c>
       <c r="B1817" t="n">
-        <v>3.289048749923556</v>
+        <v>3.289048749923555</v>
       </c>
       <c r="C1817" t="n">
         <v>3.126153974671351</v>
       </c>
       <c r="D1817" t="n">
-        <v>-0.679107173408149</v>
+        <v>-0.7360145789076363</v>
       </c>
       <c r="E1817" t="n">
-        <v>2.854154680994344</v>
+        <v>2.83139171879455</v>
       </c>
       <c r="F1817" t="n">
-        <v>1.293090190851293</v>
+        <v>1.293009417960624</v>
       </c>
       <c r="G1817" t="n">
-        <v>3.902008089182128</v>
+        <v>3.901959625447726</v>
       </c>
     </row>
     <row r="1818">
@@ -43324,22 +43324,22 @@
         <v>45280</v>
       </c>
       <c r="B1818" t="n">
-        <v>3.3080721951607</v>
+        <v>3.308072195160699</v>
       </c>
       <c r="C1818" t="n">
         <v>3.115456695754193</v>
       </c>
       <c r="D1818" t="n">
-        <v>-0.6424688506401743</v>
+        <v>-0.6993762561396617</v>
       </c>
       <c r="E1818" t="n">
-        <v>2.858112731184377</v>
+        <v>2.835349768984582</v>
       </c>
       <c r="F1818" t="n">
-        <v>1.293090190851293</v>
+        <v>1.293009417960624</v>
       </c>
       <c r="G1818" t="n">
-        <v>3.891310810264971</v>
+        <v>3.891262346530569</v>
       </c>
     </row>
     <row r="1819">
@@ -43347,22 +43347,22 @@
         <v>45281</v>
       </c>
       <c r="B1819" t="n">
-        <v>3.318993081823466</v>
+        <v>3.318993081823465</v>
       </c>
       <c r="C1819" t="n">
         <v>3.125373651216407</v>
       </c>
       <c r="D1819" t="n">
-        <v>-0.593823172170441</v>
+        <v>-0.6507305776699284</v>
       </c>
       <c r="E1819" t="n">
-        <v>2.887487958034484</v>
+        <v>2.864724995834689</v>
       </c>
       <c r="F1819" t="n">
-        <v>1.341735869321027</v>
+        <v>1.341655096430357</v>
       </c>
       <c r="G1819" t="n">
-        <v>3.930415172809025</v>
+        <v>3.930366709074623</v>
       </c>
     </row>
     <row r="1820">
@@ -43370,22 +43370,22 @@
         <v>45282</v>
       </c>
       <c r="B1820" t="n">
-        <v>3.305392684942104</v>
+        <v>3.305392684942103</v>
       </c>
       <c r="C1820" t="n">
         <v>3.132226628875955</v>
       </c>
       <c r="D1820" t="n">
-        <v>-0.5333432697510387</v>
+        <v>-0.5902506752505261</v>
       </c>
       <c r="E1820" t="n">
-        <v>2.918532896661792</v>
+        <v>2.895769934461998</v>
       </c>
       <c r="F1820" t="n">
-        <v>1.402215771740429</v>
+        <v>1.402134998849759</v>
       </c>
       <c r="G1820" t="n">
-        <v>3.973556091920214</v>
+        <v>3.973507628185811</v>
       </c>
     </row>
     <row r="1821">
@@ -43393,22 +43393,22 @@
         <v>45283</v>
       </c>
       <c r="B1821" t="n">
-        <v>3.312076663414904</v>
+        <v>3.312076663414903</v>
       </c>
       <c r="C1821" t="n">
         <v>3.134450814492048</v>
       </c>
       <c r="D1821" t="n">
-        <v>-0.4507932022349218</v>
+        <v>-0.5077006077344091</v>
       </c>
       <c r="E1821" t="n">
-        <v>2.953777109284332</v>
+        <v>2.931014147084537</v>
       </c>
       <c r="F1821" t="n">
-        <v>1.402215771740429</v>
+        <v>1.402134998849759</v>
       </c>
       <c r="G1821" t="n">
-        <v>3.975780277536307</v>
+        <v>3.975731813801905</v>
       </c>
     </row>
     <row r="1822">
@@ -43416,22 +43416,22 @@
         <v>45284</v>
       </c>
       <c r="B1822" t="n">
-        <v>3.296314293398914</v>
+        <v>3.296314293398913</v>
       </c>
       <c r="C1822" t="n">
         <v>3.121045839271831</v>
       </c>
       <c r="D1822" t="n">
-        <v>-0.3729571145397051</v>
+        <v>-0.4298645200391925</v>
       </c>
       <c r="E1822" t="n">
-        <v>2.971506569142202</v>
+        <v>2.948743606942407</v>
       </c>
       <c r="F1822" t="n">
-        <v>1.480797724396553</v>
+        <v>1.480716951505884</v>
       </c>
       <c r="G1822" t="n">
-        <v>4.009524473909765</v>
+        <v>4.009476010175363</v>
       </c>
     </row>
     <row r="1823">
@@ -43439,22 +43439,22 @@
         <v>45285</v>
       </c>
       <c r="B1823" t="n">
-        <v>3.304329929817386</v>
+        <v>3.304329929817385</v>
       </c>
       <c r="C1823" t="n">
         <v>3.126711518797542</v>
       </c>
       <c r="D1823" t="n">
-        <v>-0.2560804489247999</v>
+        <v>-0.3129878544242872</v>
       </c>
       <c r="E1823" t="n">
-        <v>3.023922914913876</v>
+        <v>3.00115995271408</v>
       </c>
       <c r="F1823" t="n">
-        <v>1.563367065856178</v>
+        <v>1.563286292965509</v>
       </c>
       <c r="G1823" t="n">
-        <v>4.064731758311251</v>
+        <v>4.064683294576849</v>
       </c>
     </row>
     <row r="1824">
@@ -43462,22 +43462,22 @@
         <v>45286</v>
       </c>
       <c r="B1824" t="n">
-        <v>3.277862502076861</v>
+        <v>3.27786250207686</v>
       </c>
       <c r="C1824" t="n">
         <v>3.130543841755795</v>
       </c>
       <c r="D1824" t="n">
-        <v>-0.1915254805680797</v>
+        <v>-0.248432886067567</v>
       </c>
       <c r="E1824" t="n">
-        <v>3.053577225214816</v>
+        <v>3.030814263015022</v>
       </c>
       <c r="F1824" t="n">
-        <v>1.627922034212899</v>
+        <v>1.627841261322229</v>
       </c>
       <c r="G1824" t="n">
-        <v>4.107297062283536</v>
+        <v>4.107248598549134</v>
       </c>
     </row>
     <row r="1825">
@@ -43491,16 +43491,16 @@
         <v>3.133773427784875</v>
       </c>
       <c r="D1825" t="n">
-        <v>-0.06541712784043285</v>
+        <v>-0.1223245333399202</v>
       </c>
       <c r="E1825" t="n">
-        <v>3.107250152334955</v>
+        <v>3.084487190135161</v>
       </c>
       <c r="F1825" t="n">
-        <v>1.627922034212899</v>
+        <v>1.627841261322229</v>
       </c>
       <c r="G1825" t="n">
-        <v>4.110526648312616</v>
+        <v>4.110478184578214</v>
       </c>
     </row>
     <row r="1826">
@@ -43508,22 +43508,22 @@
         <v>45288</v>
       </c>
       <c r="B1826" t="n">
-        <v>3.286780349061647</v>
+        <v>3.286780349061646</v>
       </c>
       <c r="C1826" t="n">
         <v>3.1338083988329</v>
       </c>
       <c r="D1826" t="n">
-        <v>0.01073793005927071</v>
+        <v>-0.0461694754402166</v>
       </c>
       <c r="E1826" t="n">
-        <v>3.137747146542862</v>
+        <v>3.114984184343067</v>
       </c>
       <c r="F1826" t="n">
-        <v>1.704077092112602</v>
+        <v>1.703996319221933</v>
       </c>
       <c r="G1826" t="n">
-        <v>4.156254654100463</v>
+        <v>4.156206190366062</v>
       </c>
     </row>
     <row r="1827">
@@ -43531,22 +43531,22 @@
         <v>45289</v>
       </c>
       <c r="B1827" t="n">
-        <v>3.170789663214113</v>
+        <v>3.172362492966895</v>
       </c>
       <c r="C1827" t="n">
         <v>3.129380481089744</v>
       </c>
       <c r="D1827" t="n">
-        <v>0.06153007419148093</v>
+        <v>0.06110917156657808</v>
       </c>
       <c r="E1827" t="n">
-        <v>3.15363608645259</v>
+        <v>3.153467725402629</v>
       </c>
       <c r="F1827" t="n">
-        <v>1.754869236244812</v>
+        <v>1.811274966228727</v>
       </c>
       <c r="G1827" t="n">
-        <v>4.182302022836633</v>
+        <v>4.216145460826982</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20231230.xlsx
+++ b/tame_output/ON/bt/strategyON_20231230.xlsx
@@ -42772,7 +42772,7 @@
         <v>45256</v>
       </c>
       <c r="B1794" t="n">
-        <v>3.147014107714845</v>
+        <v>3.147014107714844</v>
       </c>
       <c r="C1794" t="n">
         <v>3.076099785321473</v>
@@ -42910,7 +42910,7 @@
         <v>45262</v>
       </c>
       <c r="B1800" t="n">
-        <v>3.199276732583693</v>
+        <v>3.199276732583694</v>
       </c>
       <c r="C1800" t="n">
         <v>3.083027154880305</v>
@@ -42933,7 +42933,7 @@
         <v>45263</v>
       </c>
       <c r="B1801" t="n">
-        <v>3.238767863742723</v>
+        <v>3.238767863742724</v>
       </c>
       <c r="C1801" t="n">
         <v>3.090561751225397</v>
@@ -42956,7 +42956,7 @@
         <v>45264</v>
       </c>
       <c r="B1802" t="n">
-        <v>3.260068416589523</v>
+        <v>3.260068416589524</v>
       </c>
       <c r="C1802" t="n">
         <v>3.091984762198855</v>
@@ -42979,7 +42979,7 @@
         <v>45265</v>
       </c>
       <c r="B1803" t="n">
-        <v>3.306739876872956</v>
+        <v>3.306739876872957</v>
       </c>
       <c r="C1803" t="n">
         <v>3.093661836664541</v>
@@ -43002,7 +43002,7 @@
         <v>45266</v>
       </c>
       <c r="B1804" t="n">
-        <v>3.312164595946328</v>
+        <v>3.312164595946329</v>
       </c>
       <c r="C1804" t="n">
         <v>3.089601258113999</v>
@@ -43025,7 +43025,7 @@
         <v>45267</v>
       </c>
       <c r="B1805" t="n">
-        <v>3.300520058336485</v>
+        <v>3.300520058336486</v>
       </c>
       <c r="C1805" t="n">
         <v>3.094821397458016</v>
@@ -43048,7 +43048,7 @@
         <v>45268</v>
       </c>
       <c r="B1806" t="n">
-        <v>3.318449829143338</v>
+        <v>3.318449829143339</v>
       </c>
       <c r="C1806" t="n">
         <v>3.100133560631823</v>
@@ -43071,7 +43071,7 @@
         <v>45269</v>
       </c>
       <c r="B1807" t="n">
-        <v>3.311781349308502</v>
+        <v>3.311781349308503</v>
       </c>
       <c r="C1807" t="n">
         <v>3.093376148078457</v>
@@ -43094,7 +43094,7 @@
         <v>45270</v>
       </c>
       <c r="B1808" t="n">
-        <v>3.271427670257515</v>
+        <v>3.271427670257516</v>
       </c>
       <c r="C1808" t="n">
         <v>3.090839823094569</v>
@@ -43117,7 +43117,7 @@
         <v>45271</v>
       </c>
       <c r="B1809" t="n">
-        <v>3.252962387441539</v>
+        <v>3.25296238744154</v>
       </c>
       <c r="C1809" t="n">
         <v>3.109254206721308</v>
@@ -43140,7 +43140,7 @@
         <v>45272</v>
       </c>
       <c r="B1810" t="n">
-        <v>3.241257540662167</v>
+        <v>3.241257540662168</v>
       </c>
       <c r="C1810" t="n">
         <v>3.119070330776787</v>
@@ -43163,7 +43163,7 @@
         <v>45273</v>
       </c>
       <c r="B1811" t="n">
-        <v>3.285495323543323</v>
+        <v>3.285495323543324</v>
       </c>
       <c r="C1811" t="n">
         <v>3.132597942828719</v>
@@ -43186,7 +43186,7 @@
         <v>45274</v>
       </c>
       <c r="B1812" t="n">
-        <v>3.287726162978607</v>
+        <v>3.287726162978608</v>
       </c>
       <c r="C1812" t="n">
         <v>3.139185323079984</v>
@@ -43209,7 +43209,7 @@
         <v>45275</v>
       </c>
       <c r="B1813" t="n">
-        <v>3.275586179621266</v>
+        <v>3.275586179621267</v>
       </c>
       <c r="C1813" t="n">
         <v>3.128096071514691</v>
@@ -43232,7 +43232,7 @@
         <v>45276</v>
       </c>
       <c r="B1814" t="n">
-        <v>3.268822948291747</v>
+        <v>3.268822948291748</v>
       </c>
       <c r="C1814" t="n">
         <v>3.123696569025415</v>
@@ -43278,7 +43278,7 @@
         <v>45278</v>
       </c>
       <c r="B1816" t="n">
-        <v>3.291576855321622</v>
+        <v>3.291576855321623</v>
       </c>
       <c r="C1816" t="n">
         <v>3.127125924287274</v>
@@ -43301,7 +43301,7 @@
         <v>45279</v>
       </c>
       <c r="B1817" t="n">
-        <v>3.289048749923555</v>
+        <v>3.289048749923556</v>
       </c>
       <c r="C1817" t="n">
         <v>3.126153974671351</v>
@@ -43324,7 +43324,7 @@
         <v>45280</v>
       </c>
       <c r="B1818" t="n">
-        <v>3.308072195160699</v>
+        <v>3.3080721951607</v>
       </c>
       <c r="C1818" t="n">
         <v>3.115456695754193</v>
@@ -43347,7 +43347,7 @@
         <v>45281</v>
       </c>
       <c r="B1819" t="n">
-        <v>3.318993081823465</v>
+        <v>3.318993081823466</v>
       </c>
       <c r="C1819" t="n">
         <v>3.125373651216407</v>
@@ -43370,7 +43370,7 @@
         <v>45282</v>
       </c>
       <c r="B1820" t="n">
-        <v>3.305392684942103</v>
+        <v>3.305392684942104</v>
       </c>
       <c r="C1820" t="n">
         <v>3.132226628875955</v>
@@ -43393,7 +43393,7 @@
         <v>45283</v>
       </c>
       <c r="B1821" t="n">
-        <v>3.312076663414903</v>
+        <v>3.312076663414904</v>
       </c>
       <c r="C1821" t="n">
         <v>3.134450814492048</v>
@@ -43416,7 +43416,7 @@
         <v>45284</v>
       </c>
       <c r="B1822" t="n">
-        <v>3.296314293398913</v>
+        <v>3.296314293398914</v>
       </c>
       <c r="C1822" t="n">
         <v>3.121045839271831</v>
@@ -43439,7 +43439,7 @@
         <v>45285</v>
       </c>
       <c r="B1823" t="n">
-        <v>3.304329929817385</v>
+        <v>3.304329929817386</v>
       </c>
       <c r="C1823" t="n">
         <v>3.126711518797542</v>
@@ -43462,7 +43462,7 @@
         <v>45286</v>
       </c>
       <c r="B1824" t="n">
-        <v>3.27786250207686</v>
+        <v>3.277862502076861</v>
       </c>
       <c r="C1824" t="n">
         <v>3.130543841755795</v>
@@ -43508,7 +43508,7 @@
         <v>45288</v>
       </c>
       <c r="B1826" t="n">
-        <v>3.286780349061646</v>
+        <v>3.286780349061647</v>
       </c>
       <c r="C1826" t="n">
         <v>3.1338083988329</v>
@@ -43537,16 +43537,16 @@
         <v>3.129380481089744</v>
       </c>
       <c r="D1827" t="n">
-        <v>0.06110917156657808</v>
+        <v>0.06104142018278952</v>
       </c>
       <c r="E1827" t="n">
-        <v>3.153467725402629</v>
+        <v>3.153440624849114</v>
       </c>
       <c r="F1827" t="n">
-        <v>1.811274966228727</v>
+        <v>1.811207214844939</v>
       </c>
       <c r="G1827" t="n">
-        <v>4.216145460826982</v>
+        <v>4.216104809996709</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20231230.xlsx
+++ b/tame_output/ON/bt/strategyON_20231230.xlsx
@@ -901,17 +901,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-27.9%</t>
+          <t>-28.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>77.3%</t>
+          <t>77.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -992,17 +992,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-15.2%</t>
+          <t>-16.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>481.1%</t>
+          <t>479.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-136.3%</t>
+          <t>-141.3%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>71.7%</t>
+          <t>71.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1145,17 +1145,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-19.2%</t>
+          <t>-19.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-27.1%</t>
+          <t>-29.1%</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>25.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>48.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1298,17 +1298,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-28.1%</t>
+          <t>-33.1%</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>113.3%</t>
+          <t>112.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>108.5%</t>
+          <t>107.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.5%</t>
+          <t>-14.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>7.6%</t>
         </is>
       </c>
     </row>
@@ -43537,16 +43537,16 @@
         <v>3.129380481089744</v>
       </c>
       <c r="D1827" t="n">
-        <v>0.06104142018278952</v>
+        <v>0.01130118373899708</v>
       </c>
       <c r="E1827" t="n">
-        <v>3.153440624849114</v>
+        <v>3.133544530271597</v>
       </c>
       <c r="F1827" t="n">
-        <v>1.811207214844939</v>
+        <v>1.761466978401146</v>
       </c>
       <c r="G1827" t="n">
-        <v>4.216104809996709</v>
+        <v>4.186260668130434</v>
       </c>
     </row>
   </sheetData>
